--- a/LB3-Praxisarbeit/M141 LB3 Bewertung LE.xlsx
+++ b/LB3-Praxisarbeit/M141 LB3 Bewertung LE.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="C4" s="65" t="n"/>
       <c r="D4" s="66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4" s="67" t="inlineStr">
         <is>

--- a/LB3-Praxisarbeit/M141 LB3 Bewertung LE.xlsx
+++ b/LB3-Praxisarbeit/M141 LB3 Bewertung LE.xlsx
@@ -1099,7 +1099,7 @@
       <c r="E11" s="78" t="inlineStr">
         <is>
           <t>+ SMART-Anforderungen FA/NFA vollständig, Risikoanalyse
-+ Cloud-Vergleich mit gewichteter Bewertungsmatrix (4 Kandidaten)
++ Cloud-Vergleich mit gewichteter Bewertungsmatrix (5 Kandidaten)
 + Link zu Repo dokumentiert (Platzhalter)
 + Personalisierung durchgängig (gigi)</t>
         </is>
@@ -1223,10 +1223,10 @@
       </c>
       <c r="E17" s="88" t="inlineStr">
         <is>
-          <t>+ AWS RDS MariaDB 10.11 (db.t3.micro, eu-central-1)
-+ Härtung: Public Off, TLS, KMS-Encryption, Backups 7d, Deletion-Protection
-+ Custom Parameter Group dokumentiert (my_aws.cnf)
-+ Audit-Plugin (server_audit) konfiguriert</t>
+          <t xml:space="preserve">+ Eigene Cloud (Max-Bonus): MariaDB 11.8 im LXC cloud-db-giovanni auf Proxmox (Endpoint 192.168.1.62:3306)
++ Härtung: TLS erzwungen (TLSv1.3, eigene CA mit SAN), Proxmox-Firewall-Allowlist, Default-Deny
++ Setup idempotent als Script (sql/repro/setup_cloud_selfhosted.sh)
++ Doku + Live-Nachweise: MS_C_Cloud_SelfHosted.md, screenshots/cloud_*</t>
         </is>
       </c>
     </row>
@@ -1250,9 +1250,9 @@
       </c>
       <c r="E18" s="88" t="inlineStr">
         <is>
-          <t>+ 12-Punkte-Härtungs-Checkliste
-+ my_aws.cnf vollständig dokumentiert (Security/Logging/Audit)
-+ Operativer Betrieb (Backup, Monitoring, Restore-Drill) beschrieben</t>
+          <t xml:space="preserve">+ 8-Punkte-Härtungs-Checkliste, jede Massnahme einzeln live belegt (VERIFICATION.md §3)
++ config/my_cloud_selfhosted.cnf vollständig dokumentiert (TLS/Logging/Limits, local-infile=0)
++ Betrieb: Demo-Preflight (21 Checks, Auto-Heal), Golden Snapshot (Restore &lt;1 Min), Slow-/Error-Log</t>
         </is>
       </c>
     </row>
@@ -1288,9 +1288,9 @@
       </c>
       <c r="E20" s="88" t="inlineStr">
         <is>
-          <t>+ Cloud-DCL als separates Script automatisiert (03_cloud_users.sql)
-+ REQUIRE SSL für alle App-User
-+ Tests Cloud: TLS-Pflicht, Rollen-Negativ, Spaltenrechte</t>
+          <t xml:space="preserve">+ Cloud-DCL als separates Script automatisiert (sql/dcl/04_selfhosted_cloud_users.sql)
++ REQUIRE SSL für alle App-User (TLSv1.3, eigene CA, Proxmox-Firewall)
++ Tests Cloud: TLS-Pflicht (ERROR 3159), Rollen-Negativ (1142/1143), Spaltenrechte</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
           <t>+ 4 Punkte sehr gut + 1.5 Bonus (Lokal &amp; Cloud kombiniert):
   • Testprotokolle Rollen (positiv/negativ) lokal UND cloud
   • Testprotokolle Daten-Konsistenz (Import, Bereinigung, Migration)
-  • Testdaten-Generator (Personalisierung Gigi-Test)
+  • Testdaten-Generator (Personalisierung Giovanni-Test)
   • SQL-Cheat-Sheet + DQL-Reports + Performance-Stichprobe</t>
         </is>
       </c>
@@ -1440,7 +1440,7 @@
       <c r="C28" s="111" t="n"/>
       <c r="D28" s="112">
         <f>SUM(D11:D26)+D4</f>
-        <v/>
+        <v>41.5</v>
       </c>
       <c r="E28" s="113" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       <c r="C30" s="111" t="n"/>
       <c r="D30" s="120">
         <f>MIN(D28*4/44+2,6)</f>
-        <v/>
+        <v>5.7727272727272725</v>
       </c>
       <c r="E30" s="121" t="inlineStr">
         <is>

--- a/LB3-Praxisarbeit/M141 LB3 Bewertung LE.xlsx
+++ b/LB3-Praxisarbeit/M141 LB3 Bewertung LE.xlsx
@@ -1100,7 +1100,7 @@
         <is>
           <t>+ SMART-Anforderungen FA/NFA vollständig, Risikoanalyse
 + Cloud-Vergleich mit gewichteter Bewertungsmatrix (5 Kandidaten)
-+ Link zu Repo dokumentiert (Platzhalter)
++ Link zu Repo dokumentiert: github.com/LieutenantJimmy/M141 (Ordner LB3-Praxisarbeit)
 + Personalisierung durchgängig (gigi)</t>
         </is>
       </c>
